--- a/ET2/Mall-radialpumplab-VT25.xlsx
+++ b/ET2/Mall-radialpumplab-VT25.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074BDAAD-5A20-4D5A-9472-6F1E8AC411E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955232E1-96CC-471E-BC3A-D08E5343A8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
   <si>
     <t>Pin</t>
   </si>
@@ -541,12 +541,6 @@
   </si>
   <si>
     <t>60.8</t>
-  </si>
-  <si>
-    <t>39.12</t>
-  </si>
-  <si>
-    <t>38.96</t>
   </si>
 </sst>
 </file>
@@ -758,7 +752,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -869,6 +863,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1221,7 +1218,7 @@
       </c>
       <c r="G2" s="7">
         <f>AVERAGE(G5:G10)/1000</f>
-        <v>0.17933333333333334</v>
+        <v>0.17916666666666667</v>
       </c>
       <c r="H2" s="7">
         <f t="shared" ref="H2:J2" si="0">AVERAGE(H5:H10)/1000</f>
@@ -1233,7 +1230,7 @@
       </c>
       <c r="J2" s="7">
         <f t="shared" si="0"/>
-        <v>3.9219999999999998E-2</v>
+        <v>3.9100000000000003E-2</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="16.2" x14ac:dyDescent="0.25">
@@ -1297,8 +1294,8 @@
       <c r="I6" s="11">
         <v>61.1</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>121</v>
+      <c r="J6" s="11">
+        <v>39.119999999999997</v>
       </c>
       <c r="U6" s="5"/>
     </row>
@@ -1321,8 +1318,8 @@
       <c r="I7" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>122</v>
+      <c r="J7" s="11">
+        <v>38.96</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -1335,14 +1332,18 @@
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="11"/>
+      <c r="G8" s="11">
+        <v>179</v>
+      </c>
       <c r="H8" s="11">
         <v>136.5</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="J8" s="11"/>
+      <c r="J8" s="11">
+        <v>39.1</v>
+      </c>
     </row>
     <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -1355,7 +1356,9 @@
         <v>64</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="11"/>
+      <c r="G9" s="11">
+        <v>179</v>
+      </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11" t="s">
         <v>120</v>
@@ -1371,7 +1374,9 @@
         <v>3.1415926535897931</v>
       </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="11"/>
+      <c r="G10" s="11">
+        <v>179</v>
+      </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11">
         <v>60.8</v>
@@ -1514,23 +1519,32 @@
       <c r="F17" s="11">
         <v>39.1</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="52">
         <f>D17/3</f>
         <v>2219.3333333333335</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="52">
         <f>G17/1.5</f>
         <v>1479.5555555555557</v>
       </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
+      <c r="I17" s="18">
+        <f>((120*F17/2) - G17)/(120*F17/2)</f>
+        <v>5.3992611537368507E-2</v>
+      </c>
+      <c r="J17" s="52">
+        <f>((E17/1000)*Tyngdacc)/Hävarm</f>
+        <v>41.831665116279076</v>
+      </c>
       <c r="K17" s="17">
         <f>A17/1000</f>
         <v>15.6</v>
       </c>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="52">
+        <f>(G17/60)*J17</f>
+        <v>1547.3068130232564</v>
+      </c>
       <c r="O17" s="18"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -1552,23 +1566,32 @@
       <c r="F18" s="11">
         <v>39.1</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="52">
         <f t="shared" ref="G18:G26" si="1">D18/3</f>
         <v>2221.6666666666665</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="52">
         <f t="shared" ref="H18:H26" si="2">G18/1.5</f>
         <v>1481.1111111111111</v>
       </c>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
+      <c r="I18" s="18">
+        <f t="shared" ref="I18:I26" si="3">((120*F18/2) - G18)/(120*F18/2)</f>
+        <v>5.2998010798522371E-2</v>
+      </c>
+      <c r="J18" s="52">
+        <f>((E18/1000)*Tyngdacc)/Hävarm</f>
+        <v>41.776911627906976</v>
+      </c>
       <c r="K18" s="17">
-        <f t="shared" ref="K18:K26" si="3">A18/1000</f>
+        <f t="shared" ref="K18:K26" si="4">A18/1000</f>
         <v>14</v>
       </c>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
+      <c r="N18" s="52">
+        <f t="shared" ref="N18:N26" si="5">(G18/60)*J18</f>
+        <v>1546.9062000000001</v>
+      </c>
       <c r="O18" s="18"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -1590,23 +1613,32 @@
       <c r="F19" s="11">
         <v>39.1</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="52">
         <f t="shared" si="1"/>
         <v>2191</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="52">
         <f t="shared" si="2"/>
         <v>1460.6666666666667</v>
       </c>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
+      <c r="I19" s="18">
+        <f t="shared" si="3"/>
+        <v>6.6069906223358912E-2</v>
+      </c>
+      <c r="J19" s="52">
+        <f>((E19/1000)*Tyngdacc)/Hävarm</f>
+        <v>41.174623255813955</v>
+      </c>
       <c r="K19" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
+      <c r="N19" s="52">
+        <f t="shared" si="5"/>
+        <v>1503.5599925581396</v>
+      </c>
       <c r="O19" s="18"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -1628,23 +1660,32 @@
       <c r="F20" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="52">
         <f t="shared" si="1"/>
         <v>2225</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="52">
         <f t="shared" si="2"/>
         <v>1483.3333333333333</v>
       </c>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
+      <c r="I20" s="18">
+        <f t="shared" si="3"/>
+        <v>5.399659863945578E-2</v>
+      </c>
+      <c r="J20" s="52">
+        <f>((E20/1000)*Tyngdacc)/Hävarm</f>
+        <v>40.517581395348842</v>
+      </c>
       <c r="K20" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11.8</v>
       </c>
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
+      <c r="N20" s="52">
+        <f t="shared" si="5"/>
+        <v>1502.5269767441864</v>
+      </c>
       <c r="O20" s="18"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -1666,23 +1707,32 @@
       <c r="F21" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="52">
         <f t="shared" si="1"/>
         <v>2232.6666666666665</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="52">
         <f t="shared" si="2"/>
         <v>1488.4444444444443</v>
       </c>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
+      <c r="I21" s="18">
+        <f t="shared" si="3"/>
+        <v>5.0736961451247231E-2</v>
+      </c>
+      <c r="J21" s="52">
+        <f>((E21/1000)*Tyngdacc)/Hävarm</f>
+        <v>38.217934883720929</v>
+      </c>
       <c r="K21" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.5</v>
       </c>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
+      <c r="N21" s="52">
+        <f t="shared" si="5"/>
+        <v>1422.1318213953487</v>
+      </c>
       <c r="O21" s="18"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -1704,23 +1754,32 @@
       <c r="F22" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="52">
         <f t="shared" si="1"/>
         <v>2240.6666666666665</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="52">
         <f t="shared" si="2"/>
         <v>1493.7777777777776</v>
       </c>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
+      <c r="I22" s="18">
+        <f t="shared" si="3"/>
+        <v>4.733560090702954E-2</v>
+      </c>
+      <c r="J22" s="52">
+        <f>((E22/1000)*Tyngdacc)/Hävarm</f>
+        <v>36.30156279069768</v>
+      </c>
       <c r="K22" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.1</v>
       </c>
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
+      <c r="N22" s="52">
+        <f t="shared" si="5"/>
+        <v>1355.6616948837211</v>
+      </c>
       <c r="O22" s="18"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -1742,23 +1801,32 @@
       <c r="F23" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="52">
         <f t="shared" si="1"/>
         <v>2244.6666666666665</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="52">
         <f t="shared" si="2"/>
         <v>1496.4444444444443</v>
       </c>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
+      <c r="I23" s="18">
+        <f t="shared" si="3"/>
+        <v>4.5634920634920702E-2</v>
+      </c>
+      <c r="J23" s="52">
+        <f>((E23/1000)*Tyngdacc)/Hävarm</f>
+        <v>35.042232558139538</v>
+      </c>
       <c r="K23" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2</v>
       </c>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
+      <c r="N23" s="52">
+        <f t="shared" si="5"/>
+        <v>1310.9688558139537</v>
+      </c>
       <c r="O23" s="18"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -1780,23 +1848,32 @@
       <c r="F24" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="52">
         <f t="shared" si="1"/>
         <v>2248.6666666666665</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="52">
         <f t="shared" si="2"/>
         <v>1499.1111111111111</v>
       </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
+      <c r="I24" s="18">
+        <f t="shared" si="3"/>
+        <v>4.3934240362811856E-2</v>
+      </c>
+      <c r="J24" s="52">
+        <f>((E24/1000)*Tyngdacc)/Hävarm</f>
+        <v>33.837655813953489</v>
+      </c>
       <c r="K24" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.4</v>
       </c>
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
+      <c r="N24" s="52">
+        <f t="shared" si="5"/>
+        <v>1268.160145116279</v>
+      </c>
       <c r="O24" s="18"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -1818,23 +1895,32 @@
       <c r="F25" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="52">
         <f t="shared" si="1"/>
         <v>2254.6666666666665</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="52">
         <f t="shared" si="2"/>
         <v>1503.1111111111111</v>
       </c>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
+      <c r="I25" s="18">
+        <f t="shared" si="3"/>
+        <v>4.1383219954648588E-2</v>
+      </c>
+      <c r="J25" s="52">
+        <f>((E25/1000)*Tyngdacc)/Hävarm</f>
+        <v>32.304558139534883</v>
+      </c>
       <c r="K25" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.5</v>
       </c>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
+      <c r="N25" s="52">
+        <f t="shared" si="5"/>
+        <v>1213.9335069767442</v>
+      </c>
       <c r="O25" s="18"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -1856,23 +1942,32 @@
       <c r="F26" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="52">
         <f t="shared" si="1"/>
         <v>2261.3333333333335</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="52">
         <f t="shared" si="2"/>
         <v>1507.5555555555557</v>
       </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
+      <c r="I26" s="18">
+        <f t="shared" si="3"/>
+        <v>3.8548752834467057E-2</v>
+      </c>
+      <c r="J26" s="52">
+        <f>((E26/1000)*Tyngdacc)/Hävarm</f>
+        <v>30.661953488372095</v>
+      </c>
       <c r="K26" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8</v>
       </c>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
+      <c r="N26" s="52">
+        <f t="shared" si="5"/>
+        <v>1155.614958139535</v>
+      </c>
       <c r="O26" s="18"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -2021,23 +2116,32 @@
       <c r="F32" s="11">
         <v>31.3</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="52">
         <f>D32/3</f>
         <v>1780.6666666666667</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="52">
         <f>G32/1.5</f>
         <v>1187.1111111111111</v>
       </c>
-      <c r="I32" s="18"/>
-      <c r="J32" s="17"/>
+      <c r="I32" s="18">
+        <f>((120*F32/2) - G32)/(120*F32/2)</f>
+        <v>5.1828186013489486E-2</v>
+      </c>
+      <c r="J32" s="52">
+        <f>((E32/1000)*Tyngdacc)/Hävarm</f>
+        <v>30.661953488372095</v>
+      </c>
       <c r="K32" s="17">
         <f>A32/1000</f>
         <v>12.4</v>
       </c>
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
+      <c r="N32" s="52">
+        <f>(G32/60)*J32</f>
+        <v>909.97864186046525</v>
+      </c>
       <c r="O32" s="18"/>
       <c r="P32" s="12"/>
       <c r="Q32" s="12"/>
@@ -2062,23 +2166,32 @@
       <c r="F33" s="11">
         <v>31.3</v>
       </c>
-      <c r="G33" s="17">
-        <f t="shared" ref="G33:G41" si="4">D33/3</f>
+      <c r="G33" s="52">
+        <f t="shared" ref="G33:G41" si="6">D33/3</f>
         <v>1782.6666666666667</v>
       </c>
-      <c r="H33" s="17">
-        <f t="shared" ref="H33:H41" si="5">G33/1.5</f>
+      <c r="H33" s="52">
+        <f t="shared" ref="H33:H41" si="7">G33/1.5</f>
         <v>1188.4444444444446</v>
       </c>
-      <c r="I33" s="18"/>
-      <c r="J33" s="17"/>
+      <c r="I33" s="18">
+        <f t="shared" ref="I33:I41" si="8">((120*F33/2) - G33)/(120*F33/2)</f>
+        <v>5.0763223287184911E-2</v>
+      </c>
+      <c r="J33" s="52">
+        <f>((E33/1000)*Tyngdacc)/Hävarm</f>
+        <v>30.388186046511631</v>
+      </c>
       <c r="K33" s="17">
-        <f t="shared" ref="K33:K41" si="6">A33/1000</f>
+        <f t="shared" ref="K33:K41" si="9">A33/1000</f>
         <v>11.4</v>
       </c>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
+      <c r="N33" s="52">
+        <f t="shared" ref="N33:N41" si="10">(G33/60)*J33</f>
+        <v>902.86677209302343</v>
+      </c>
       <c r="O33" s="18"/>
       <c r="P33" s="12"/>
       <c r="Q33" s="12"/>
@@ -2103,23 +2216,32 @@
       <c r="F34" s="11">
         <v>31.3</v>
       </c>
-      <c r="G34" s="17">
-        <f t="shared" si="4"/>
+      <c r="G34" s="52">
+        <f t="shared" si="6"/>
         <v>1784</v>
       </c>
-      <c r="H34" s="17">
-        <f t="shared" si="5"/>
+      <c r="H34" s="52">
+        <f t="shared" si="7"/>
         <v>1189.3333333333333</v>
       </c>
-      <c r="I34" s="18"/>
-      <c r="J34" s="17"/>
+      <c r="I34" s="18">
+        <f t="shared" si="8"/>
+        <v>5.0053248136315232E-2</v>
+      </c>
+      <c r="J34" s="52">
+        <f>((E34/1000)*Tyngdacc)/Hävarm</f>
+        <v>29.840651162790703</v>
+      </c>
       <c r="K34" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
+      <c r="N34" s="52">
+        <f t="shared" si="10"/>
+        <v>887.26202790697698</v>
+      </c>
       <c r="O34" s="18"/>
       <c r="P34" s="12"/>
       <c r="Q34" s="12"/>
@@ -2144,23 +2266,32 @@
       <c r="F35" s="11">
         <v>31.3</v>
       </c>
-      <c r="G35" s="17">
-        <f t="shared" si="4"/>
+      <c r="G35" s="52">
+        <f t="shared" si="6"/>
         <v>1791.6666666666667</v>
       </c>
-      <c r="H35" s="17">
-        <f t="shared" si="5"/>
+      <c r="H35" s="52">
+        <f t="shared" si="7"/>
         <v>1194.4444444444446</v>
       </c>
-      <c r="I35" s="18"/>
-      <c r="J35" s="17"/>
+      <c r="I35" s="18">
+        <f t="shared" si="8"/>
+        <v>4.5970891018814304E-2</v>
+      </c>
+      <c r="J35" s="52">
+        <f>((E35/1000)*Tyngdacc)/Hävarm</f>
+        <v>29.183609302325586</v>
+      </c>
       <c r="K35" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9.6</v>
       </c>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
+      <c r="N35" s="52">
+        <f t="shared" si="10"/>
+        <v>871.45500000000015</v>
+      </c>
       <c r="O35" s="18"/>
       <c r="P35" s="12"/>
       <c r="Q35" s="12"/>
@@ -2185,23 +2316,32 @@
       <c r="F36" s="11">
         <v>31.3</v>
       </c>
-      <c r="G36" s="17">
-        <f t="shared" si="4"/>
+      <c r="G36" s="52">
+        <f t="shared" si="6"/>
         <v>1789.6666666666667</v>
       </c>
-      <c r="H36" s="17">
-        <f t="shared" si="5"/>
+      <c r="H36" s="52">
+        <f t="shared" si="7"/>
         <v>1193.1111111111111</v>
       </c>
-      <c r="I36" s="18"/>
-      <c r="J36" s="17"/>
+      <c r="I36" s="18">
+        <f t="shared" si="8"/>
+        <v>4.7035853745118879E-2</v>
+      </c>
+      <c r="J36" s="52">
+        <f>((E36/1000)*Tyngdacc)/Hävarm</f>
+        <v>28.745581395348839</v>
+      </c>
       <c r="K36" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>8.6999999999999993</v>
       </c>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
+      <c r="N36" s="52">
+        <f t="shared" si="10"/>
+        <v>857.41681395348849</v>
+      </c>
       <c r="O36" s="18"/>
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
@@ -2226,23 +2366,32 @@
       <c r="F37" s="11">
         <v>31.3</v>
       </c>
-      <c r="G37" s="17">
-        <f t="shared" si="4"/>
+      <c r="G37" s="52">
+        <f t="shared" si="6"/>
         <v>1791</v>
       </c>
-      <c r="H37" s="17">
-        <f t="shared" si="5"/>
+      <c r="H37" s="52">
+        <f t="shared" si="7"/>
         <v>1194</v>
       </c>
-      <c r="I37" s="18"/>
-      <c r="J37" s="17"/>
+      <c r="I37" s="18">
+        <f t="shared" si="8"/>
+        <v>4.6325878594249199E-2</v>
+      </c>
+      <c r="J37" s="52">
+        <f>((E37/1000)*Tyngdacc)/Hävarm</f>
+        <v>27.924279069767447</v>
+      </c>
       <c r="K37" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>7.9</v>
       </c>
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
+      <c r="N37" s="52">
+        <f t="shared" si="10"/>
+        <v>833.53973023255833</v>
+      </c>
       <c r="O37" s="18"/>
       <c r="P37" s="12"/>
       <c r="Q37" s="12"/>
@@ -2267,23 +2416,32 @@
       <c r="F38" s="11">
         <v>31.3</v>
       </c>
-      <c r="G38" s="17">
-        <f t="shared" si="4"/>
+      <c r="G38" s="52">
+        <f t="shared" si="6"/>
         <v>1794.6666666666667</v>
       </c>
-      <c r="H38" s="17">
-        <f t="shared" si="5"/>
+      <c r="H38" s="52">
+        <f t="shared" si="7"/>
         <v>1196.4444444444446</v>
       </c>
-      <c r="I38" s="18"/>
-      <c r="J38" s="17"/>
+      <c r="I38" s="18">
+        <f t="shared" si="8"/>
+        <v>4.4373446929357435E-2</v>
+      </c>
+      <c r="J38" s="52">
+        <f>((E38/1000)*Tyngdacc)/Hävarm</f>
+        <v>27.376744186046512</v>
+      </c>
       <c r="K38" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
+      <c r="N38" s="52">
+        <f t="shared" si="10"/>
+        <v>818.86883720930234</v>
+      </c>
       <c r="O38" s="18"/>
       <c r="P38" s="12"/>
       <c r="Q38" s="12"/>
@@ -2308,23 +2466,32 @@
       <c r="F39" s="11">
         <v>31.3</v>
       </c>
-      <c r="G39" s="17">
-        <f t="shared" si="4"/>
+      <c r="G39" s="52">
+        <f t="shared" si="6"/>
         <v>1798</v>
       </c>
-      <c r="H39" s="17">
-        <f t="shared" si="5"/>
+      <c r="H39" s="52">
+        <f t="shared" si="7"/>
         <v>1198.6666666666667</v>
       </c>
-      <c r="I39" s="18"/>
-      <c r="J39" s="17"/>
+      <c r="I39" s="18">
+        <f t="shared" si="8"/>
+        <v>4.2598509052183174E-2</v>
+      </c>
+      <c r="J39" s="52">
+        <f>((E39/1000)*Tyngdacc)/Hävarm</f>
+        <v>26.445934883720927</v>
+      </c>
       <c r="K39" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.2</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
+      <c r="N39" s="52">
+        <f t="shared" si="10"/>
+        <v>792.49651534883708</v>
+      </c>
       <c r="O39" s="18"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -2346,23 +2513,32 @@
       <c r="F40" s="11">
         <v>31.4</v>
       </c>
-      <c r="G40" s="17">
-        <f t="shared" si="4"/>
+      <c r="G40" s="52">
+        <f t="shared" si="6"/>
         <v>1801.3333333333333</v>
       </c>
-      <c r="H40" s="17">
-        <f t="shared" si="5"/>
+      <c r="H40" s="52">
+        <f t="shared" si="7"/>
         <v>1200.8888888888889</v>
       </c>
-      <c r="I40" s="18"/>
-      <c r="J40" s="17"/>
+      <c r="I40" s="18">
+        <f t="shared" si="8"/>
+        <v>4.3878273177636276E-2</v>
+      </c>
+      <c r="J40" s="52">
+        <f>((E40/1000)*Tyngdacc)/Hävarm</f>
+        <v>25.241358139534888</v>
+      </c>
       <c r="K40" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.4</v>
       </c>
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
+      <c r="N40" s="52">
+        <f t="shared" si="10"/>
+        <v>757.80166325581411</v>
+      </c>
       <c r="O40" s="18"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -2384,23 +2560,32 @@
       <c r="F41" s="11">
         <v>31.4</v>
       </c>
-      <c r="G41" s="17">
-        <f t="shared" si="4"/>
+      <c r="G41" s="52">
+        <f t="shared" si="6"/>
         <v>1806</v>
       </c>
-      <c r="H41" s="17">
-        <f t="shared" si="5"/>
+      <c r="H41" s="52">
+        <f t="shared" si="7"/>
         <v>1204</v>
       </c>
-      <c r="I41" s="18"/>
-      <c r="J41" s="17"/>
+      <c r="I41" s="18">
+        <f t="shared" si="8"/>
+        <v>4.1401273885350316E-2</v>
+      </c>
+      <c r="J41" s="52">
+        <f>((E41/1000)*Tyngdacc)/Hävarm</f>
+        <v>24.091534883720932</v>
+      </c>
       <c r="K41" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
+      <c r="N41" s="52">
+        <f t="shared" si="10"/>
+        <v>725.15520000000015</v>
+      </c>
       <c r="O41" s="18"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -3123,11 +3308,11 @@
         <v>0.01</v>
       </c>
       <c r="B84" s="37" t="e">
-        <f t="shared" ref="B84:B85" si="7">4*Densitet*A84/3600/PI()/RörDiam_sug/Dynamisk_viskositet</f>
+        <f t="shared" ref="B84:B85" si="11">4*Densitet*A84/3600/PI()/RörDiam_sug/Dynamisk_viskositet</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C84" s="37" t="e">
-        <f t="shared" ref="C84:C85" si="8">4*Densitet*A84/3600/PI()/RörDiam_tryck/Dynamisk_viskositet</f>
+        <f t="shared" ref="C84:C85" si="12">4*Densitet*A84/3600/PI()/RörDiam_tryck/Dynamisk_viskositet</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D84" s="17"/>
@@ -3144,11 +3329,11 @@
         <v>1</v>
       </c>
       <c r="B85" s="37" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="C85" s="37" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D85" s="17"/>

--- a/ET2/Mall-radialpumplab-VT25.xlsx
+++ b/ET2/Mall-radialpumplab-VT25.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955232E1-96CC-471E-BC3A-D08E5343A8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02D3EF4-E8FD-446C-AC09-6AACAC066762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1528,22 +1528,25 @@
         <v>1479.5555555555557</v>
       </c>
       <c r="I17" s="18">
-        <f>((120*F17/2) - G17)/(120*F17/2)</f>
-        <v>5.3992611537368507E-2</v>
+        <f>1-(G17/(30*2*F17))</f>
+        <v>5.3992611537368451E-2</v>
       </c>
       <c r="J17" s="52">
-        <f>((E17/1000)*Tyngdacc)/Hävarm</f>
-        <v>41.831665116279076</v>
+        <f>((E17/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.3428255000000002</v>
       </c>
       <c r="K17" s="17">
         <f>A17/1000</f>
         <v>15.6</v>
       </c>
-      <c r="L17" s="17"/>
+      <c r="L17" s="17">
+        <f>delta_z+((C17-ABS(B17/10))/(Densitet*Tyngdacc))</f>
+        <v>0.13936635201772976</v>
+      </c>
       <c r="M17" s="17"/>
       <c r="N17" s="52">
         <f>(G17/60)*J17</f>
-        <v>1547.3068130232564</v>
+        <v>49.669623216666679</v>
       </c>
       <c r="O17" s="18"/>
     </row>
@@ -1575,12 +1578,12 @@
         <v>1481.1111111111111</v>
       </c>
       <c r="I18" s="18">
-        <f t="shared" ref="I18:I26" si="3">((120*F18/2) - G18)/(120*F18/2)</f>
-        <v>5.2998010798522371E-2</v>
+        <f t="shared" ref="I18:I26" si="3">1-(G18/(30*2*F18))</f>
+        <v>5.2998010798522399E-2</v>
       </c>
       <c r="J18" s="52">
-        <f>((E18/1000)*Tyngdacc)/Hävarm</f>
-        <v>41.776911627906976</v>
+        <f>((E18/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.341067875</v>
       </c>
       <c r="K18" s="17">
         <f t="shared" ref="K18:K26" si="4">A18/1000</f>
@@ -1590,7 +1593,7 @@
       <c r="M18" s="17"/>
       <c r="N18" s="52">
         <f t="shared" ref="N18:N26" si="5">(G18/60)*J18</f>
-        <v>1546.9062000000001</v>
+        <v>49.656763260416668</v>
       </c>
       <c r="O18" s="18"/>
     </row>
@@ -1623,11 +1626,11 @@
       </c>
       <c r="I19" s="18">
         <f t="shared" si="3"/>
-        <v>6.6069906223358912E-2</v>
+        <v>6.6069906223358954E-2</v>
       </c>
       <c r="J19" s="52">
-        <f>((E19/1000)*Tyngdacc)/Hävarm</f>
-        <v>41.174623255813955</v>
+        <f>((E19/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.3217340000000002</v>
       </c>
       <c r="K19" s="17">
         <f t="shared" si="4"/>
@@ -1637,7 +1640,7 @@
       <c r="M19" s="17"/>
       <c r="N19" s="52">
         <f t="shared" si="5"/>
-        <v>1503.5599925581396</v>
+        <v>48.265319900000009</v>
       </c>
       <c r="O19" s="18"/>
     </row>
@@ -1670,11 +1673,11 @@
       </c>
       <c r="I20" s="18">
         <f t="shared" si="3"/>
-        <v>5.399659863945578E-2</v>
+        <v>5.3996598639455828E-2</v>
       </c>
       <c r="J20" s="52">
-        <f>((E20/1000)*Tyngdacc)/Hävarm</f>
-        <v>40.517581395348842</v>
+        <f>((E20/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.3006425000000001</v>
       </c>
       <c r="K20" s="17">
         <f t="shared" si="4"/>
@@ -1684,7 +1687,7 @@
       <c r="M20" s="17"/>
       <c r="N20" s="52">
         <f t="shared" si="5"/>
-        <v>1502.5269767441864</v>
+        <v>48.232159375000009</v>
       </c>
       <c r="O20" s="18"/>
     </row>
@@ -1717,11 +1720,11 @@
       </c>
       <c r="I21" s="18">
         <f t="shared" si="3"/>
-        <v>5.0736961451247231E-2</v>
+        <v>5.0736961451247176E-2</v>
       </c>
       <c r="J21" s="52">
-        <f>((E21/1000)*Tyngdacc)/Hävarm</f>
-        <v>38.217934883720929</v>
+        <f>((E21/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.2268222500000001</v>
       </c>
       <c r="K21" s="17">
         <f t="shared" si="4"/>
@@ -1731,7 +1734,7 @@
       <c r="M21" s="17"/>
       <c r="N21" s="52">
         <f t="shared" si="5"/>
-        <v>1422.1318213953487</v>
+        <v>45.651419058333332</v>
       </c>
       <c r="O21" s="18"/>
     </row>
@@ -1764,11 +1767,11 @@
       </c>
       <c r="I22" s="18">
         <f t="shared" si="3"/>
-        <v>4.733560090702954E-2</v>
+        <v>4.7335600907029596E-2</v>
       </c>
       <c r="J22" s="52">
-        <f>((E22/1000)*Tyngdacc)/Hävarm</f>
-        <v>36.30156279069768</v>
+        <f>((E22/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.1653053750000002</v>
       </c>
       <c r="K22" s="17">
         <f t="shared" si="4"/>
@@ -1778,7 +1781,7 @@
       <c r="M22" s="17"/>
       <c r="N22" s="52">
         <f t="shared" si="5"/>
-        <v>1355.6616948837211</v>
+        <v>43.517681837500007</v>
       </c>
       <c r="O22" s="18"/>
     </row>
@@ -1811,11 +1814,11 @@
       </c>
       <c r="I23" s="18">
         <f t="shared" si="3"/>
-        <v>4.5634920634920702E-2</v>
+        <v>4.5634920634920695E-2</v>
       </c>
       <c r="J23" s="52">
-        <f>((E23/1000)*Tyngdacc)/Hävarm</f>
-        <v>35.042232558139538</v>
+        <f>((E23/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.1248800000000001</v>
       </c>
       <c r="K23" s="17">
         <f t="shared" si="4"/>
@@ -1825,7 +1828,7 @@
       <c r="M23" s="17"/>
       <c r="N23" s="52">
         <f t="shared" si="5"/>
-        <v>1310.9688558139537</v>
+        <v>42.083010666666674</v>
       </c>
       <c r="O23" s="18"/>
     </row>
@@ -1858,11 +1861,11 @@
       </c>
       <c r="I24" s="18">
         <f t="shared" si="3"/>
-        <v>4.3934240362811856E-2</v>
+        <v>4.3934240362811905E-2</v>
       </c>
       <c r="J24" s="52">
-        <f>((E24/1000)*Tyngdacc)/Hävarm</f>
-        <v>33.837655813953489</v>
+        <f>((E24/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.0862122500000002</v>
       </c>
       <c r="K24" s="17">
         <f t="shared" si="4"/>
@@ -1872,7 +1875,7 @@
       <c r="M24" s="17"/>
       <c r="N24" s="52">
         <f t="shared" si="5"/>
-        <v>1268.160145116279</v>
+        <v>40.708821325000002</v>
       </c>
       <c r="O24" s="18"/>
     </row>
@@ -1905,11 +1908,11 @@
       </c>
       <c r="I25" s="18">
         <f t="shared" si="3"/>
-        <v>4.1383219954648588E-2</v>
+        <v>4.1383219954648554E-2</v>
       </c>
       <c r="J25" s="52">
-        <f>((E25/1000)*Tyngdacc)/Hävarm</f>
-        <v>32.304558139534883</v>
+        <f>((E25/1000)*Tyngdacc)*Hävarm</f>
+        <v>1.03699875</v>
       </c>
       <c r="K25" s="17">
         <f t="shared" si="4"/>
@@ -1919,7 +1922,7 @@
       <c r="M25" s="17"/>
       <c r="N25" s="52">
         <f t="shared" si="5"/>
-        <v>1213.9335069767442</v>
+        <v>38.968108583333333</v>
       </c>
       <c r="O25" s="18"/>
     </row>
@@ -1952,11 +1955,11 @@
       </c>
       <c r="I26" s="18">
         <f t="shared" si="3"/>
-        <v>3.8548752834467057E-2</v>
+        <v>3.8548752834467015E-2</v>
       </c>
       <c r="J26" s="52">
-        <f>((E26/1000)*Tyngdacc)/Hävarm</f>
-        <v>30.661953488372095</v>
+        <f>((E26/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.98427000000000009</v>
       </c>
       <c r="K26" s="17">
         <f t="shared" si="4"/>
@@ -1966,7 +1969,7 @@
       <c r="M26" s="17"/>
       <c r="N26" s="52">
         <f t="shared" si="5"/>
-        <v>1155.614958139535</v>
+        <v>37.096042666666669</v>
       </c>
       <c r="O26" s="18"/>
     </row>
@@ -2125,12 +2128,12 @@
         <v>1187.1111111111111</v>
       </c>
       <c r="I32" s="18">
-        <f>((120*F32/2) - G32)/(120*F32/2)</f>
+        <f>1-(G32/(30*2*F32))</f>
         <v>5.1828186013489486E-2</v>
       </c>
       <c r="J32" s="52">
-        <f>((E32/1000)*Tyngdacc)/Hävarm</f>
-        <v>30.661953488372095</v>
+        <f>((E32/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.98427000000000009</v>
       </c>
       <c r="K32" s="17">
         <f>A32/1000</f>
@@ -2140,7 +2143,7 @@
       <c r="M32" s="17"/>
       <c r="N32" s="52">
         <f>(G32/60)*J32</f>
-        <v>909.97864186046525</v>
+        <v>29.210946333333339</v>
       </c>
       <c r="O32" s="18"/>
       <c r="P32" s="12"/>
@@ -2175,12 +2178,12 @@
         <v>1188.4444444444446</v>
       </c>
       <c r="I33" s="18">
-        <f t="shared" ref="I33:I41" si="8">((120*F33/2) - G33)/(120*F33/2)</f>
-        <v>5.0763223287184911E-2</v>
+        <f t="shared" ref="I33:I41" si="8">1-(G33/(30*2*F33))</f>
+        <v>5.0763223287184855E-2</v>
       </c>
       <c r="J33" s="52">
-        <f>((E33/1000)*Tyngdacc)/Hävarm</f>
-        <v>30.388186046511631</v>
+        <f>((E33/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.97548187500000005</v>
       </c>
       <c r="K33" s="17">
         <f t="shared" ref="K33:K41" si="9">A33/1000</f>
@@ -2190,7 +2193,7 @@
       <c r="M33" s="17"/>
       <c r="N33" s="52">
         <f t="shared" ref="N33:N41" si="10">(G33/60)*J33</f>
-        <v>902.86677209302343</v>
+        <v>28.982650375000002</v>
       </c>
       <c r="O33" s="18"/>
       <c r="P33" s="12"/>
@@ -2226,11 +2229,11 @@
       </c>
       <c r="I34" s="18">
         <f t="shared" si="8"/>
-        <v>5.0053248136315232E-2</v>
+        <v>5.0053248136315176E-2</v>
       </c>
       <c r="J34" s="52">
-        <f>((E34/1000)*Tyngdacc)/Hävarm</f>
-        <v>29.840651162790703</v>
+        <f>((E34/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.9579056250000002</v>
       </c>
       <c r="K34" s="17">
         <f t="shared" si="9"/>
@@ -2240,7 +2243,7 @@
       <c r="M34" s="17"/>
       <c r="N34" s="52">
         <f t="shared" si="10"/>
-        <v>887.26202790697698</v>
+        <v>28.481727250000006</v>
       </c>
       <c r="O34" s="18"/>
       <c r="P34" s="12"/>
@@ -2276,11 +2279,11 @@
       </c>
       <c r="I35" s="18">
         <f t="shared" si="8"/>
-        <v>4.5970891018814304E-2</v>
+        <v>4.5970891018814353E-2</v>
       </c>
       <c r="J35" s="52">
-        <f>((E35/1000)*Tyngdacc)/Hävarm</f>
-        <v>29.183609302325586</v>
+        <f>((E35/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.93681412500000005</v>
       </c>
       <c r="K35" s="17">
         <f t="shared" si="9"/>
@@ -2290,7 +2293,7 @@
       <c r="M35" s="17"/>
       <c r="N35" s="52">
         <f t="shared" si="10"/>
-        <v>871.45500000000015</v>
+        <v>27.974310677083334</v>
       </c>
       <c r="O35" s="18"/>
       <c r="P35" s="12"/>
@@ -2326,11 +2329,11 @@
       </c>
       <c r="I36" s="18">
         <f t="shared" si="8"/>
-        <v>4.7035853745118879E-2</v>
+        <v>4.7035853745118872E-2</v>
       </c>
       <c r="J36" s="52">
-        <f>((E36/1000)*Tyngdacc)/Hävarm</f>
-        <v>28.745581395348839</v>
+        <f>((E36/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.92275312500000017</v>
       </c>
       <c r="K36" s="17">
         <f t="shared" si="9"/>
@@ -2340,7 +2343,7 @@
       <c r="M36" s="17"/>
       <c r="N36" s="52">
         <f t="shared" si="10"/>
-        <v>857.41681395348849</v>
+        <v>27.523675156250007</v>
       </c>
       <c r="O36" s="18"/>
       <c r="P36" s="12"/>
@@ -2376,11 +2379,11 @@
       </c>
       <c r="I37" s="18">
         <f t="shared" si="8"/>
-        <v>4.6325878594249199E-2</v>
+        <v>4.6325878594249192E-2</v>
       </c>
       <c r="J37" s="52">
-        <f>((E37/1000)*Tyngdacc)/Hävarm</f>
-        <v>27.924279069767447</v>
+        <f>((E37/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.89638875000000018</v>
       </c>
       <c r="K37" s="17">
         <f t="shared" si="9"/>
@@ -2390,7 +2393,7 @@
       <c r="M37" s="17"/>
       <c r="N37" s="52">
         <f t="shared" si="10"/>
-        <v>833.53973023255833</v>
+        <v>26.757204187500008</v>
       </c>
       <c r="O37" s="18"/>
       <c r="P37" s="12"/>
@@ -2426,11 +2429,11 @@
       </c>
       <c r="I38" s="18">
         <f t="shared" si="8"/>
-        <v>4.4373446929357435E-2</v>
+        <v>4.4373446929357407E-2</v>
       </c>
       <c r="J38" s="52">
-        <f>((E38/1000)*Tyngdacc)/Hävarm</f>
-        <v>27.376744186046512</v>
+        <f>((E38/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.87881250000000011</v>
       </c>
       <c r="K38" s="17">
         <f t="shared" si="9"/>
@@ -2440,7 +2443,7 @@
       <c r="M38" s="17"/>
       <c r="N38" s="52">
         <f t="shared" si="10"/>
-        <v>818.86883720930234</v>
+        <v>26.286258333333336</v>
       </c>
       <c r="O38" s="18"/>
       <c r="P38" s="12"/>
@@ -2476,11 +2479,11 @@
       </c>
       <c r="I39" s="18">
         <f t="shared" si="8"/>
-        <v>4.2598509052183174E-2</v>
+        <v>4.2598509052183209E-2</v>
       </c>
       <c r="J39" s="52">
-        <f>((E39/1000)*Tyngdacc)/Hävarm</f>
-        <v>26.445934883720927</v>
+        <f>((E39/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.84893287499999992</v>
       </c>
       <c r="K39" s="17">
         <f t="shared" si="9"/>
@@ -2490,7 +2493,7 @@
       <c r="M39" s="17"/>
       <c r="N39" s="52">
         <f t="shared" si="10"/>
-        <v>792.49651534883708</v>
+        <v>25.439688487499996</v>
       </c>
       <c r="O39" s="18"/>
     </row>
@@ -2523,11 +2526,11 @@
       </c>
       <c r="I40" s="18">
         <f t="shared" si="8"/>
-        <v>4.3878273177636276E-2</v>
+        <v>4.3878273177636262E-2</v>
       </c>
       <c r="J40" s="52">
-        <f>((E40/1000)*Tyngdacc)/Hävarm</f>
-        <v>25.241358139534888</v>
+        <f>((E40/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.81026512500000014</v>
       </c>
       <c r="K40" s="17">
         <f t="shared" si="9"/>
@@ -2537,7 +2540,7 @@
       <c r="M40" s="17"/>
       <c r="N40" s="52">
         <f t="shared" si="10"/>
-        <v>757.80166325581411</v>
+        <v>24.325959641666671</v>
       </c>
       <c r="O40" s="18"/>
     </row>
@@ -2570,11 +2573,11 @@
       </c>
       <c r="I41" s="18">
         <f t="shared" si="8"/>
-        <v>4.1401273885350316E-2</v>
+        <v>4.1401273885350309E-2</v>
       </c>
       <c r="J41" s="52">
-        <f>((E41/1000)*Tyngdacc)/Hävarm</f>
-        <v>24.091534883720932</v>
+        <f>((E41/1000)*Tyngdacc)*Hävarm</f>
+        <v>0.77335500000000013</v>
       </c>
       <c r="K41" s="17">
         <f t="shared" si="9"/>
@@ -2584,7 +2587,7 @@
       <c r="M41" s="17"/>
       <c r="N41" s="52">
         <f t="shared" si="10"/>
-        <v>725.15520000000015</v>
+        <v>23.277985500000003</v>
       </c>
       <c r="O41" s="18"/>
     </row>

--- a/ET2/Mall-radialpumplab-VT25.xlsx
+++ b/ET2/Mall-radialpumplab-VT25.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02D3EF4-E8FD-446C-AC09-6AACAC066762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DC66CE-9C1F-4E77-B556-2EE23FEB83BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1176,6 +1176,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{BAD0D276-5BD5-4AB3-9093-ED2DA379A4EC}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="WA200010725" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U187"/>
@@ -1539,16 +1559,22 @@
         <f>A17/1000</f>
         <v>15.6</v>
       </c>
-      <c r="L17" s="17">
-        <f>delta_z+((C17-ABS(B17/10))/(Densitet*Tyngdacc))</f>
-        <v>0.13936635201772976</v>
-      </c>
-      <c r="M17" s="17"/>
+      <c r="L17" s="52">
+        <f>delta_z+((C17-ABS(B17/10))*1000/(Densitet*Tyngdacc))+(((4*(K17/3600))/(π*PumpDiam_tryck^2))^2-((4*(K17/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>2.6801323564454522</v>
+      </c>
+      <c r="M17" s="52">
+        <f>Densitet*Tyngdacc*(K17/3600)*L17</f>
+        <v>113.72734810484567</v>
+      </c>
       <c r="N17" s="52">
-        <f>(G17/60)*J17</f>
-        <v>49.669623216666679</v>
-      </c>
-      <c r="O17" s="18"/>
+        <f>((G17*2*π)/60)*J17</f>
+        <v>312.08344680810615</v>
+      </c>
+      <c r="O17" s="18">
+        <f>M17/N17</f>
+        <v>0.36441326596464546</v>
+      </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
@@ -1582,20 +1608,29 @@
         <v>5.2998010798522399E-2</v>
       </c>
       <c r="J18" s="52">
-        <f>((E18/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" ref="J17:J26" si="4">((E18/1000)*Tyngdacc)*Hävarm</f>
         <v>1.341067875</v>
       </c>
       <c r="K18" s="17">
-        <f t="shared" ref="K18:K26" si="4">A18/1000</f>
+        <f t="shared" ref="K18:K26" si="5">A18/1000</f>
         <v>14</v>
       </c>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
+      <c r="L18" s="52">
+        <f>delta_z+((C18-ABS(B18/10))*1000/(Densitet*Tyngdacc))+(((4*(K18/3600))/(π*PumpDiam_tryck^2))^2-((4*(K18/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>3.6195603366657756</v>
+      </c>
+      <c r="M18" s="52">
+        <f>Densitet*Tyngdacc*(K18/3600)*L18</f>
+        <v>137.83767163548052</v>
+      </c>
       <c r="N18" s="52">
-        <f t="shared" ref="N18:N26" si="5">(G18/60)*J18</f>
-        <v>49.656763260416668</v>
-      </c>
-      <c r="O18" s="18"/>
+        <f>((G18*2*π)/60)*J18</f>
+        <v>312.00264531994503</v>
+      </c>
+      <c r="O18" s="18">
+        <f t="shared" ref="O18:O26" si="6">M18/N18</f>
+        <v>0.44178366338571917</v>
+      </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
@@ -1629,20 +1664,29 @@
         <v>6.6069906223358954E-2</v>
       </c>
       <c r="J19" s="52">
-        <f>((E19/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="4"/>
         <v>1.3217340000000002</v>
       </c>
       <c r="K19" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
+      <c r="L19" s="52">
+        <f>delta_z+((C19-ABS(B19/10))*1000/(Densitet*Tyngdacc))+(((4*(K19/3600))/(π*PumpDiam_tryck^2))^2-((4*(K19/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>4.028138543801326</v>
+      </c>
+      <c r="M19" s="52">
+        <f>Densitet*Tyngdacc*(K19/3600)*L19</f>
+        <v>142.43995365991648</v>
+      </c>
       <c r="N19" s="52">
-        <f t="shared" si="5"/>
-        <v>48.265319900000009</v>
-      </c>
-      <c r="O19" s="18"/>
+        <f>((G19*2*π)/60)*J19</f>
+        <v>303.25994884200253</v>
+      </c>
+      <c r="O19" s="18">
+        <f t="shared" si="6"/>
+        <v>0.46969589688260233</v>
+      </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
@@ -1676,20 +1720,29 @@
         <v>5.3996598639455828E-2</v>
       </c>
       <c r="J20" s="52">
-        <f>((E20/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="4"/>
         <v>1.3006425000000001</v>
       </c>
       <c r="K20" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.8</v>
       </c>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
+      <c r="L20" s="52">
+        <f>delta_z+((C20-ABS(B20/10))*1000/(Densitet*Tyngdacc))+(((4*(K20/3600))/(π*PumpDiam_tryck^2))^2-((4*(K20/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>4.4151450476493777</v>
+      </c>
+      <c r="M20" s="52">
+        <f>Densitet*Tyngdacc*(K20/3600)*L20</f>
+        <v>141.71344482695284</v>
+      </c>
       <c r="N20" s="52">
-        <f t="shared" si="5"/>
-        <v>48.232159375000009</v>
-      </c>
-      <c r="O20" s="18"/>
+        <f>((G20*2*π)/60)*J20</f>
+        <v>303.05159511854418</v>
+      </c>
+      <c r="O20" s="18">
+        <f t="shared" si="6"/>
+        <v>0.46762151102197308</v>
+      </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
@@ -1723,20 +1776,29 @@
         <v>5.0736961451247176E-2</v>
       </c>
       <c r="J21" s="52">
-        <f>((E21/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="4"/>
         <v>1.2268222500000001</v>
       </c>
       <c r="K21" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.5</v>
       </c>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
+      <c r="L21" s="52">
+        <f>delta_z+((C21-ABS(B21/10))*1000/(Densitet*Tyngdacc))+(((4*(K21/3600))/(π*PumpDiam_tryck^2))^2-((4*(K21/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>5.1415325087880728</v>
+      </c>
+      <c r="M21" s="52">
+        <f>Densitet*Tyngdacc*(K21/3600)*L21</f>
+        <v>132.86184026017298</v>
+      </c>
       <c r="N21" s="52">
-        <f t="shared" si="5"/>
-        <v>45.651419058333332</v>
-      </c>
-      <c r="O21" s="18"/>
+        <f>((G21*2*π)/60)*J21</f>
+        <v>286.83632547921815</v>
+      </c>
+      <c r="O21" s="18">
+        <f t="shared" si="6"/>
+        <v>0.46319740025326422</v>
+      </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
@@ -1770,20 +1832,29 @@
         <v>4.7335600907029596E-2</v>
       </c>
       <c r="J22" s="52">
-        <f>((E22/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="4"/>
         <v>1.1653053750000002</v>
       </c>
       <c r="K22" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.1</v>
       </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
+      <c r="L22" s="52">
+        <f>delta_z+((C22-ABS(B22/10))*1000/(Densitet*Tyngdacc))+(((4*(K22/3600))/(π*PumpDiam_tryck^2))^2-((4*(K22/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>5.545245944725572</v>
+      </c>
+      <c r="M22" s="52">
+        <f>Densitet*Tyngdacc*(K22/3600)*L22</f>
+        <v>122.17712572094827</v>
+      </c>
       <c r="N22" s="52">
-        <f t="shared" si="5"/>
-        <v>43.517681837500007</v>
-      </c>
-      <c r="O22" s="18"/>
+        <f>((G22*2*π)/60)*J22</f>
+        <v>273.42965912389593</v>
+      </c>
+      <c r="O22" s="18">
+        <f t="shared" si="6"/>
+        <v>0.44683201563582975</v>
+      </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
@@ -1817,20 +1888,29 @@
         <v>4.5634920634920695E-2</v>
       </c>
       <c r="J23" s="52">
-        <f>((E23/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="4"/>
         <v>1.1248800000000001</v>
       </c>
       <c r="K23" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.2</v>
       </c>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
+      <c r="L23" s="52">
+        <f>delta_z+((C23-ABS(B23/10))*1000/(Densitet*Tyngdacc))+(((4*(K23/3600))/(π*PumpDiam_tryck^2))^2-((4*(K23/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>5.6978629738682693</v>
+      </c>
+      <c r="M23" s="52">
+        <f>Densitet*Tyngdacc*(K23/3600)*L23</f>
+        <v>111.59084581851033</v>
+      </c>
       <c r="N23" s="52">
-        <f t="shared" si="5"/>
-        <v>42.083010666666674</v>
-      </c>
-      <c r="O23" s="18"/>
+        <f>((G23*2*π)/60)*J23</f>
+        <v>264.41535430268181</v>
+      </c>
+      <c r="O23" s="18">
+        <f t="shared" si="6"/>
+        <v>0.42202861521714036</v>
+      </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
@@ -1864,20 +1944,29 @@
         <v>4.3934240362811905E-2</v>
       </c>
       <c r="J24" s="52">
-        <f>((E24/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="4"/>
         <v>1.0862122500000002</v>
       </c>
       <c r="K24" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.4</v>
       </c>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
+      <c r="L24" s="52">
+        <f>delta_z+((C24-ABS(B24/10))*1000/(Densitet*Tyngdacc))+(((4*(K24/3600))/(π*PumpDiam_tryck^2))^2-((4*(K24/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>5.8468161063589337</v>
+      </c>
+      <c r="M24" s="52">
+        <f>Densitet*Tyngdacc*(K24/3600)*L24</f>
+        <v>101.78492964368898</v>
+      </c>
       <c r="N24" s="52">
-        <f t="shared" si="5"/>
-        <v>40.708821325000002</v>
-      </c>
-      <c r="O24" s="18"/>
+        <f>((G24*2*π)/60)*J24</f>
+        <v>255.78106802183905</v>
+      </c>
+      <c r="O24" s="18">
+        <f t="shared" si="6"/>
+        <v>0.3979376989504102</v>
+      </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
@@ -1911,20 +2000,29 @@
         <v>4.1383219954648554E-2</v>
       </c>
       <c r="J25" s="52">
-        <f>((E25/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="4"/>
         <v>1.03699875</v>
       </c>
       <c r="K25" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.5</v>
       </c>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
+      <c r="L25" s="52">
+        <f>delta_z+((C25-ABS(B25/10))*1000/(Densitet*Tyngdacc))+(((4*(K25/3600))/(π*PumpDiam_tryck^2))^2-((4*(K25/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>5.9859423633953535</v>
+      </c>
+      <c r="M25" s="52">
+        <f>Densitet*Tyngdacc*(K25/3600)*L25</f>
+        <v>89.552825411279372</v>
+      </c>
       <c r="N25" s="52">
-        <f t="shared" si="5"/>
-        <v>38.968108583333333</v>
-      </c>
-      <c r="O25" s="18"/>
+        <f>((G25*2*π)/60)*J25</f>
+        <v>244.84384729937869</v>
+      </c>
+      <c r="O25" s="18">
+        <f t="shared" si="6"/>
+        <v>0.36575485314025541</v>
+      </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
@@ -1958,20 +2056,29 @@
         <v>3.8548752834467015E-2</v>
       </c>
       <c r="J26" s="52">
-        <f>((E26/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="4"/>
         <v>0.98427000000000009</v>
       </c>
       <c r="K26" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8</v>
       </c>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
+      <c r="L26" s="52">
+        <f>delta_z+((C26-ABS(B26/10))*1000/(Densitet*Tyngdacc))+(((4*(K26/3600))/(π*PumpDiam_tryck^2))^2-((4*(K26/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>6.0308783077437287</v>
+      </c>
+      <c r="M26" s="52">
+        <f>Densitet*Tyngdacc*(K26/3600)*L26</f>
+        <v>78.741897266410461</v>
+      </c>
       <c r="N26" s="52">
-        <f t="shared" si="5"/>
-        <v>37.096042666666669</v>
-      </c>
-      <c r="O26" s="18"/>
+        <f>((G26*2*π)/60)*J26</f>
+        <v>233.08131023770704</v>
+      </c>
+      <c r="O26" s="18">
+        <f t="shared" si="6"/>
+        <v>0.33783016401489185</v>
+      </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E27" s="5"/>
@@ -2132,20 +2239,29 @@
         <v>5.1828186013489486E-2</v>
       </c>
       <c r="J32" s="52">
-        <f>((E32/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" ref="J32:J41" si="7">((E32/1000)*Tyngdacc)*Hävarm</f>
         <v>0.98427000000000009</v>
       </c>
       <c r="K32" s="17">
         <f>A32/1000</f>
         <v>12.4</v>
       </c>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
+      <c r="L32" s="52">
+        <f>delta_z+((C32-ABS(B32/10))*1000/(Densitet*Tyngdacc))+(((4*(K32/3600))/(π*PumpDiam_tryck^2))^2-((4*(K32/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>1.9256652561505403</v>
+      </c>
+      <c r="M32" s="52">
+        <f>Densitet*Tyngdacc*(K32/3600)*L32</f>
+        <v>64.951106193117184</v>
+      </c>
       <c r="N32" s="52">
-        <f>(G32/60)*J32</f>
-        <v>29.210946333333339</v>
-      </c>
-      <c r="O32" s="18"/>
+        <f>((G32*2*π)/60)*J32</f>
+        <v>183.53778881041143</v>
+      </c>
+      <c r="O32" s="18">
+        <f>M32/N32</f>
+        <v>0.35388410536104675</v>
+      </c>
       <c r="P32" s="12"/>
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
@@ -2170,32 +2286,41 @@
         <v>31.3</v>
       </c>
       <c r="G33" s="52">
-        <f t="shared" ref="G33:G41" si="6">D33/3</f>
+        <f t="shared" ref="G33:G41" si="8">D33/3</f>
         <v>1782.6666666666667</v>
       </c>
       <c r="H33" s="52">
-        <f t="shared" ref="H33:H41" si="7">G33/1.5</f>
+        <f t="shared" ref="H33:H41" si="9">G33/1.5</f>
         <v>1188.4444444444446</v>
       </c>
       <c r="I33" s="18">
-        <f t="shared" ref="I33:I41" si="8">1-(G33/(30*2*F33))</f>
+        <f t="shared" ref="I33:I41" si="10">1-(G33/(30*2*F33))</f>
         <v>5.0763223287184855E-2</v>
       </c>
       <c r="J33" s="52">
-        <f>((E33/1000)*Tyngdacc)*Hävarm</f>
+        <f t="shared" si="7"/>
         <v>0.97548187500000005</v>
       </c>
       <c r="K33" s="17">
-        <f t="shared" ref="K33:K41" si="9">A33/1000</f>
+        <f t="shared" ref="K33:K41" si="11">A33/1000</f>
         <v>11.4</v>
       </c>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
+      <c r="L33" s="52">
+        <f>delta_z+((C33-ABS(B33/10))*1000/(Densitet*Tyngdacc))+(((4*(K33/3600))/(π*PumpDiam_tryck^2))^2-((4*(K33/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>2.2393734102889775</v>
+      </c>
+      <c r="M33" s="52">
+        <f>Densitet*Tyngdacc*(K33/3600)*L33</f>
+        <v>69.440915947643958</v>
+      </c>
       <c r="N33" s="52">
-        <f t="shared" ref="N33:N41" si="10">(G33/60)*J33</f>
-        <v>28.982650375000002</v>
-      </c>
-      <c r="O33" s="18"/>
+        <f>((G33*2*π)/60)*J33</f>
+        <v>182.10336299932291</v>
+      </c>
+      <c r="O33" s="18">
+        <f t="shared" ref="O33:O41" si="12">M33/N33</f>
+        <v>0.38132692776191152</v>
+      </c>
       <c r="P33" s="12"/>
       <c r="Q33" s="12"/>
       <c r="R33" s="12"/>
@@ -2220,32 +2345,41 @@
         <v>31.3</v>
       </c>
       <c r="G34" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1784</v>
       </c>
       <c r="H34" s="52">
+        <f t="shared" si="9"/>
+        <v>1189.3333333333333</v>
+      </c>
+      <c r="I34" s="18">
+        <f t="shared" si="10"/>
+        <v>5.0053248136315176E-2</v>
+      </c>
+      <c r="J34" s="52">
         <f t="shared" si="7"/>
-        <v>1189.3333333333333</v>
-      </c>
-      <c r="I34" s="18">
-        <f t="shared" si="8"/>
-        <v>5.0053248136315176E-2</v>
-      </c>
-      <c r="J34" s="52">
-        <f>((E34/1000)*Tyngdacc)*Hävarm</f>
         <v>0.9579056250000002</v>
       </c>
       <c r="K34" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10.5</v>
       </c>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
+      <c r="L34" s="52">
+        <f>delta_z+((C34-ABS(B34/10))*1000/(Densitet*Tyngdacc))+(((4*(K34/3600))/(π*PumpDiam_tryck^2))^2-((4*(K34/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>2.5725607522704208</v>
+      </c>
+      <c r="M34" s="52">
+        <f>Densitet*Tyngdacc*(K34/3600)*L34</f>
+        <v>73.474901214193608</v>
+      </c>
       <c r="N34" s="52">
-        <f t="shared" si="10"/>
-        <v>28.481727250000006</v>
-      </c>
-      <c r="O34" s="18"/>
+        <f>((G34*2*π)/60)*J34</f>
+        <v>178.95597018029648</v>
+      </c>
+      <c r="O34" s="18">
+        <f t="shared" si="12"/>
+        <v>0.41057530039466317</v>
+      </c>
       <c r="P34" s="12"/>
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
@@ -2270,32 +2404,41 @@
         <v>31.3</v>
       </c>
       <c r="G35" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1791.6666666666667</v>
       </c>
       <c r="H35" s="52">
+        <f t="shared" si="9"/>
+        <v>1194.4444444444446</v>
+      </c>
+      <c r="I35" s="18">
+        <f t="shared" si="10"/>
+        <v>4.5970891018814353E-2</v>
+      </c>
+      <c r="J35" s="52">
         <f t="shared" si="7"/>
-        <v>1194.4444444444446</v>
-      </c>
-      <c r="I35" s="18">
-        <f t="shared" si="8"/>
-        <v>4.5970891018814353E-2</v>
-      </c>
-      <c r="J35" s="52">
-        <f>((E35/1000)*Tyngdacc)*Hävarm</f>
         <v>0.93681412500000005</v>
       </c>
       <c r="K35" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>9.6</v>
       </c>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
+      <c r="L35" s="52">
+        <f>delta_z+((C35-ABS(B35/10))*1000/(Densitet*Tyngdacc))+(((4*(K35/3600))/(π*PumpDiam_tryck^2))^2-((4*(K35/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>2.8992066302914452</v>
+      </c>
+      <c r="M35" s="52">
+        <f>Densitet*Tyngdacc*(K35/3600)*L35</f>
+        <v>75.706727606617051</v>
+      </c>
       <c r="N35" s="52">
-        <f t="shared" si="10"/>
-        <v>27.974310677083334</v>
-      </c>
-      <c r="O35" s="18"/>
+        <f>((G35*2*π)/60)*J35</f>
+        <v>175.76777782472703</v>
+      </c>
+      <c r="O35" s="18">
+        <f t="shared" si="12"/>
+        <v>0.43072017262521606</v>
+      </c>
       <c r="P35" s="12"/>
       <c r="Q35" s="12"/>
       <c r="R35" s="12"/>
@@ -2320,32 +2463,41 @@
         <v>31.3</v>
       </c>
       <c r="G36" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1789.6666666666667</v>
       </c>
       <c r="H36" s="52">
+        <f t="shared" si="9"/>
+        <v>1193.1111111111111</v>
+      </c>
+      <c r="I36" s="18">
+        <f t="shared" si="10"/>
+        <v>4.7035853745118872E-2</v>
+      </c>
+      <c r="J36" s="52">
         <f t="shared" si="7"/>
-        <v>1193.1111111111111</v>
-      </c>
-      <c r="I36" s="18">
-        <f t="shared" si="8"/>
-        <v>4.7035853745118872E-2</v>
-      </c>
-      <c r="J36" s="52">
-        <f>((E36/1000)*Tyngdacc)*Hävarm</f>
         <v>0.92275312500000017</v>
       </c>
       <c r="K36" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>8.6999999999999993</v>
       </c>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
+      <c r="L36" s="52">
+        <f>delta_z+((C36-ABS(B36/10))*1000/(Densitet*Tyngdacc))+(((4*(K36/3600))/(π*PumpDiam_tryck^2))^2-((4*(K36/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>3.1376145513169842</v>
+      </c>
+      <c r="M36" s="52">
+        <f>Densitet*Tyngdacc*(K36/3600)*L36</f>
+        <v>74.251103980791768</v>
+      </c>
       <c r="N36" s="52">
-        <f t="shared" si="10"/>
-        <v>27.523675156250007</v>
-      </c>
-      <c r="O36" s="18"/>
+        <f>((G36*2*π)/60)*J36</f>
+        <v>172.93635134133385</v>
+      </c>
+      <c r="O36" s="18">
+        <f t="shared" si="12"/>
+        <v>0.42935509743835371</v>
+      </c>
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
       <c r="R36" s="12"/>
@@ -2370,32 +2522,41 @@
         <v>31.3</v>
       </c>
       <c r="G37" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1791</v>
       </c>
       <c r="H37" s="52">
+        <f t="shared" si="9"/>
+        <v>1194</v>
+      </c>
+      <c r="I37" s="18">
+        <f t="shared" si="10"/>
+        <v>4.6325878594249192E-2</v>
+      </c>
+      <c r="J37" s="52">
         <f t="shared" si="7"/>
-        <v>1194</v>
-      </c>
-      <c r="I37" s="18">
-        <f t="shared" si="8"/>
-        <v>4.6325878594249192E-2</v>
-      </c>
-      <c r="J37" s="52">
-        <f>((E37/1000)*Tyngdacc)*Hävarm</f>
         <v>0.89638875000000018</v>
       </c>
       <c r="K37" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>7.9</v>
       </c>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
+      <c r="L37" s="52">
+        <f>delta_z+((C37-ABS(B37/10))*1000/(Densitet*Tyngdacc))+(((4*(K37/3600))/(π*PumpDiam_tryck^2))^2-((4*(K37/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>3.2913418229644917</v>
+      </c>
+      <c r="M37" s="52">
+        <f>Densitet*Tyngdacc*(K37/3600)*L37</f>
+        <v>70.726823243899133</v>
+      </c>
       <c r="N37" s="52">
-        <f t="shared" si="10"/>
-        <v>26.757204187500008</v>
-      </c>
-      <c r="O37" s="18"/>
+        <f>((G37*2*π)/60)*J37</f>
+        <v>168.12047221210412</v>
+      </c>
+      <c r="O37" s="18">
+        <f t="shared" si="12"/>
+        <v>0.42069131922654113</v>
+      </c>
       <c r="P37" s="12"/>
       <c r="Q37" s="12"/>
       <c r="R37" s="12"/>
@@ -2420,32 +2581,41 @@
         <v>31.3</v>
       </c>
       <c r="G38" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1794.6666666666667</v>
       </c>
       <c r="H38" s="52">
+        <f t="shared" si="9"/>
+        <v>1196.4444444444446</v>
+      </c>
+      <c r="I38" s="18">
+        <f t="shared" si="10"/>
+        <v>4.4373446929357407E-2</v>
+      </c>
+      <c r="J38" s="52">
         <f t="shared" si="7"/>
-        <v>1196.4444444444446</v>
-      </c>
-      <c r="I38" s="18">
-        <f t="shared" si="8"/>
-        <v>4.4373446929357407E-2</v>
-      </c>
-      <c r="J38" s="52">
-        <f>((E38/1000)*Tyngdacc)*Hävarm</f>
         <v>0.87881250000000011</v>
       </c>
       <c r="K38" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
+      <c r="L38" s="52">
+        <f>delta_z+((C38-ABS(B38/10))*1000/(Densitet*Tyngdacc))+(((4*(K38/3600))/(π*PumpDiam_tryck^2))^2-((4*(K38/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>3.4447745404780696</v>
+      </c>
+      <c r="M38" s="52">
+        <f>Densitet*Tyngdacc*(K38/3600)*L38</f>
+        <v>65.590798025771861</v>
+      </c>
       <c r="N38" s="52">
-        <f t="shared" si="10"/>
-        <v>26.286258333333336</v>
-      </c>
-      <c r="O38" s="18"/>
+        <f>((G38*2*π)/60)*J38</f>
+        <v>165.16143214072699</v>
+      </c>
+      <c r="O38" s="18">
+        <f t="shared" si="12"/>
+        <v>0.39713144391896982</v>
+      </c>
       <c r="P38" s="12"/>
       <c r="Q38" s="12"/>
       <c r="R38" s="12"/>
@@ -2470,32 +2640,41 @@
         <v>31.3</v>
       </c>
       <c r="G39" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1798</v>
       </c>
       <c r="H39" s="52">
+        <f t="shared" si="9"/>
+        <v>1198.6666666666667</v>
+      </c>
+      <c r="I39" s="18">
+        <f t="shared" si="10"/>
+        <v>4.2598509052183209E-2</v>
+      </c>
+      <c r="J39" s="52">
         <f t="shared" si="7"/>
-        <v>1198.6666666666667</v>
-      </c>
-      <c r="I39" s="18">
-        <f t="shared" si="8"/>
-        <v>4.2598509052183209E-2</v>
-      </c>
-      <c r="J39" s="52">
-        <f>((E39/1000)*Tyngdacc)*Hävarm</f>
         <v>0.84893287499999992</v>
       </c>
       <c r="K39" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.2</v>
       </c>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
+      <c r="L39" s="52">
+        <f>delta_z+((C39-ABS(B39/10))*1000/(Densitet*Tyngdacc))+(((4*(K39/3600))/(π*PumpDiam_tryck^2))^2-((4*(K39/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>3.6046647909277905</v>
+      </c>
+      <c r="M39" s="52">
+        <f>Densitet*Tyngdacc*(K39/3600)*L39</f>
+        <v>60.791190181768123</v>
+      </c>
       <c r="N39" s="52">
-        <f t="shared" si="10"/>
-        <v>25.439688487499996</v>
-      </c>
-      <c r="O39" s="18"/>
+        <f>((G39*2*π)/60)*J39</f>
+        <v>159.84227692388566</v>
+      </c>
+      <c r="O39" s="18">
+        <f t="shared" si="12"/>
+        <v>0.38031984623639914</v>
+      </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
@@ -2517,32 +2696,41 @@
         <v>31.4</v>
       </c>
       <c r="G40" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1801.3333333333333</v>
       </c>
       <c r="H40" s="52">
+        <f t="shared" si="9"/>
+        <v>1200.8888888888889</v>
+      </c>
+      <c r="I40" s="18">
+        <f t="shared" si="10"/>
+        <v>4.3878273177636262E-2</v>
+      </c>
+      <c r="J40" s="52">
         <f t="shared" si="7"/>
-        <v>1200.8888888888889</v>
-      </c>
-      <c r="I40" s="18">
-        <f t="shared" si="8"/>
-        <v>4.3878273177636262E-2</v>
-      </c>
-      <c r="J40" s="52">
-        <f>((E40/1000)*Tyngdacc)*Hävarm</f>
         <v>0.81026512500000014</v>
       </c>
       <c r="K40" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5.4</v>
       </c>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
+      <c r="L40" s="52">
+        <f>delta_z+((C40-ABS(B40/10))*1000/(Densitet*Tyngdacc))+(((4*(K40/3600))/(π*PumpDiam_tryck^2))^2-((4*(K40/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>3.6653346504023654</v>
+      </c>
+      <c r="M40" s="52">
+        <f>Densitet*Tyngdacc*(K40/3600)*L40</f>
+        <v>53.8383156617856</v>
+      </c>
       <c r="N40" s="52">
-        <f t="shared" si="10"/>
-        <v>24.325959641666671</v>
-      </c>
-      <c r="O40" s="18"/>
+        <f>((G40*2*π)/60)*J40</f>
+        <v>152.84451220356362</v>
+      </c>
+      <c r="O40" s="18">
+        <f t="shared" si="12"/>
+        <v>0.35224238597511348</v>
+      </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
@@ -2564,32 +2752,41 @@
         <v>31.4</v>
       </c>
       <c r="G41" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1806</v>
       </c>
       <c r="H41" s="52">
+        <f t="shared" si="9"/>
+        <v>1204</v>
+      </c>
+      <c r="I41" s="18">
+        <f t="shared" si="10"/>
+        <v>4.1401273885350309E-2</v>
+      </c>
+      <c r="J41" s="52">
         <f t="shared" si="7"/>
-        <v>1204</v>
-      </c>
-      <c r="I41" s="18">
-        <f t="shared" si="8"/>
-        <v>4.1401273885350309E-2</v>
-      </c>
-      <c r="J41" s="52">
-        <f>((E41/1000)*Tyngdacc)*Hävarm</f>
         <v>0.77335500000000013</v>
       </c>
       <c r="K41" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
+      <c r="L41" s="52">
+        <f>delta_z+((C41-ABS(B41/10))*1000/(Densitet*Tyngdacc))+(((4*(K41/3600))/(π*PumpDiam_tryck^2))^2-((4*(K41/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
+        <v>3.8065227863762909</v>
+      </c>
+      <c r="M41" s="52">
+        <f>Densitet*Tyngdacc*(K41/3600)*L41</f>
+        <v>45.558055833876168</v>
+      </c>
       <c r="N41" s="52">
-        <f t="shared" si="10"/>
-        <v>23.277985500000003</v>
-      </c>
-      <c r="O41" s="18"/>
+        <f>((G41*2*π)/60)*J41</f>
+        <v>146.25989647433946</v>
+      </c>
+      <c r="O41" s="18">
+        <f t="shared" si="12"/>
+        <v>0.31148699631323129</v>
+      </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E42" s="5"/>
@@ -3311,11 +3508,11 @@
         <v>0.01</v>
       </c>
       <c r="B84" s="37" t="e">
-        <f t="shared" ref="B84:B85" si="11">4*Densitet*A84/3600/PI()/RörDiam_sug/Dynamisk_viskositet</f>
+        <f t="shared" ref="B84:B85" si="13">4*Densitet*A84/3600/PI()/RörDiam_sug/Dynamisk_viskositet</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C84" s="37" t="e">
-        <f t="shared" ref="C84:C85" si="12">4*Densitet*A84/3600/PI()/RörDiam_tryck/Dynamisk_viskositet</f>
+        <f t="shared" ref="C84:C85" si="14">4*Densitet*A84/3600/PI()/RörDiam_tryck/Dynamisk_viskositet</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D84" s="17"/>
@@ -3332,11 +3529,11 @@
         <v>1</v>
       </c>
       <c r="B85" s="37" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="C85" s="37" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D85" s="17"/>
